--- a/data/Terre di Pedemonte/investment_decision/Cavigliano_MFH_until_2004_investment_decision.xlsx
+++ b/data/Terre di Pedemonte/investment_decision/Cavigliano_MFH_until_2004_investment_decision.xlsx
@@ -461,22 +461,22 @@
       </c>
       <c r="F1" s="1" t="inlineStr">
         <is>
+          <t>scen_cp_dr_invested_available_unit</t>
+        </is>
+      </c>
+      <c r="G1" s="1" t="inlineStr">
+        <is>
+          <t>scen_cp_dr_candidate_unit</t>
+        </is>
+      </c>
+      <c r="H1" s="1" t="inlineStr">
+        <is>
           <t>scen_cp_cu_invested_available_unit</t>
         </is>
       </c>
-      <c r="G1" s="1" t="inlineStr">
+      <c r="I1" s="1" t="inlineStr">
         <is>
           <t>scen_cp_cu_candidate_unit</t>
-        </is>
-      </c>
-      <c r="H1" s="1" t="inlineStr">
-        <is>
-          <t>scen_cp_dr_invested_available_unit</t>
-        </is>
-      </c>
-      <c r="I1" s="1" t="inlineStr">
-        <is>
-          <t>scen_cp_dr_candidate_unit</t>
         </is>
       </c>
       <c r="J1" s="1" t="inlineStr">
@@ -495,7 +495,7 @@
         <v>46023</v>
       </c>
       <c r="B2" t="n">
-        <v>7.069743495203978</v>
+        <v>6.730910847324643</v>
       </c>
       <c r="C2" t="inlineStr">
         <is>
@@ -509,19 +509,19 @@
         <v>16642.60573452693</v>
       </c>
       <c r="F2" t="n">
-        <v>7.069743495203978</v>
+        <v>6.743060461122193</v>
       </c>
       <c r="G2" t="n">
         <v>16642.60573452693</v>
       </c>
       <c r="H2" t="n">
-        <v>5.868015317460326</v>
+        <v>6.730910847324643</v>
       </c>
       <c r="I2" t="n">
         <v>16642.60573452693</v>
       </c>
       <c r="J2" t="n">
-        <v>5.868015317460323</v>
+        <v>7.14781204058341</v>
       </c>
       <c r="K2" t="n">
         <v>16642.60573452693</v>
@@ -532,7 +532,7 @@
         <v>47849</v>
       </c>
       <c r="B3" t="n">
-        <v>51.4278947696593</v>
+        <v>28.14812386198394</v>
       </c>
       <c r="C3" t="inlineStr">
         <is>
@@ -546,19 +546,19 @@
         <v>16642.60573452693</v>
       </c>
       <c r="F3" t="n">
-        <v>56.92409821622932</v>
+        <v>32.36966200813759</v>
       </c>
       <c r="G3" t="n">
         <v>16642.60573452693</v>
       </c>
       <c r="H3" t="n">
-        <v>50.70260362433167</v>
+        <v>28.1481238619839</v>
       </c>
       <c r="I3" t="n">
         <v>16642.60573452693</v>
       </c>
       <c r="J3" t="n">
-        <v>56.92409821622932</v>
+        <v>32.67323981908293</v>
       </c>
       <c r="K3" t="n">
         <v>16642.60573452693</v>
@@ -569,7 +569,7 @@
         <v>49675</v>
       </c>
       <c r="B4" t="n">
-        <v>54.89998302948549</v>
+        <v>51.72858806666935</v>
       </c>
       <c r="C4" t="inlineStr">
         <is>
@@ -583,19 +583,19 @@
         <v>16642.60573452693</v>
       </c>
       <c r="F4" t="n">
-        <v>67.74710371377</v>
+        <v>52.92075391002198</v>
       </c>
       <c r="G4" t="n">
         <v>16642.60573452693</v>
       </c>
       <c r="H4" t="n">
-        <v>54.8999830294855</v>
+        <v>53.01645138395097</v>
       </c>
       <c r="I4" t="n">
         <v>16642.60573452693</v>
       </c>
       <c r="J4" t="n">
-        <v>68.10304629941071</v>
+        <v>52.68890578126451</v>
       </c>
       <c r="K4" t="n">
         <v>16642.60573452693</v>
@@ -606,7 +606,7 @@
         <v>51502</v>
       </c>
       <c r="B5" t="n">
-        <v>54.89998302948549</v>
+        <v>58.54967911368935</v>
       </c>
       <c r="C5" t="inlineStr">
         <is>
@@ -620,19 +620,19 @@
         <v>16642.60573452693</v>
       </c>
       <c r="F5" t="n">
-        <v>67.74710371377</v>
+        <v>58.54539849401968</v>
       </c>
       <c r="G5" t="n">
         <v>16642.60573452693</v>
       </c>
       <c r="H5" t="n">
-        <v>54.8999830294855</v>
+        <v>53.01645138395097</v>
       </c>
       <c r="I5" t="n">
         <v>16642.60573452693</v>
       </c>
       <c r="J5" t="n">
-        <v>68.10304629941071</v>
+        <v>52.68890578126451</v>
       </c>
       <c r="K5" t="n">
         <v>16642.60573452693</v>
@@ -643,7 +643,7 @@
         <v>53328</v>
       </c>
       <c r="B6" t="n">
-        <v>61.5546183854941</v>
+        <v>58.54967911368936</v>
       </c>
       <c r="C6" t="inlineStr">
         <is>
@@ -657,19 +657,19 @@
         <v>16642.60573452693</v>
       </c>
       <c r="F6" t="n">
-        <v>67.74710371377</v>
+        <v>58.54539849401969</v>
       </c>
       <c r="G6" t="n">
         <v>16642.60573452693</v>
       </c>
       <c r="H6" t="n">
-        <v>61.5546183854941</v>
+        <v>53.29027252310748</v>
       </c>
       <c r="I6" t="n">
         <v>16642.60573452693</v>
       </c>
       <c r="J6" t="n">
-        <v>68.10304629941071</v>
+        <v>53.22886795165416</v>
       </c>
       <c r="K6" t="n">
         <v>16642.60573452693</v>
@@ -684,32 +684,32 @@
       </c>
       <c r="C7" t="inlineStr">
         <is>
-          <t>BLVL_VanadiumRedox_s_2 MWh_d_Cavigliano_b_MFH_until_2004</t>
+          <t>BLVL_Li-ion_s_12.5 kWh_d_Cavigliano_b_MFH_until_2004</t>
         </is>
       </c>
       <c r="D7" t="n">
-        <v>2</v>
+        <v>0.0125</v>
       </c>
       <c r="E7" t="n">
-        <v>24.96390860179039</v>
+        <v>35.94603160112359</v>
       </c>
       <c r="F7" t="n">
         <v>0</v>
       </c>
       <c r="G7" t="n">
-        <v>14.21593463717053</v>
+        <v>35.94603160112359</v>
       </c>
       <c r="H7" t="n">
         <v>0</v>
       </c>
       <c r="I7" t="n">
-        <v>24.96390860179039</v>
+        <v>20.46980878910086</v>
       </c>
       <c r="J7" t="n">
         <v>0</v>
       </c>
       <c r="K7" t="n">
-        <v>14.21593463717053</v>
+        <v>20.46980878910086</v>
       </c>
     </row>
     <row r="8">
@@ -721,32 +721,32 @@
       </c>
       <c r="C8" t="inlineStr">
         <is>
-          <t>BLVL_VanadiumRedox_s_2 MWh_d_Cavigliano_b_MFH_until_2004</t>
+          <t>BLVL_Li-ion_s_12.5 kWh_d_Cavigliano_b_MFH_until_2004</t>
         </is>
       </c>
       <c r="D8" t="n">
-        <v>2</v>
+        <v>0.0125</v>
       </c>
       <c r="E8" t="n">
-        <v>24.96390860179039</v>
+        <v>35.94603160112359</v>
       </c>
       <c r="F8" t="n">
         <v>0</v>
       </c>
       <c r="G8" t="n">
-        <v>17.30483193025488</v>
+        <v>35.94603160112359</v>
       </c>
       <c r="H8" t="n">
         <v>0</v>
       </c>
       <c r="I8" t="n">
-        <v>24.96390860179039</v>
+        <v>24.91757381984896</v>
       </c>
       <c r="J8" t="n">
         <v>0</v>
       </c>
       <c r="K8" t="n">
-        <v>17.30483193025488</v>
+        <v>24.91757381984896</v>
       </c>
     </row>
     <row r="9">
@@ -758,32 +758,32 @@
       </c>
       <c r="C9" t="inlineStr">
         <is>
-          <t>BLVL_VanadiumRedox_s_2 MWh_d_Cavigliano_b_MFH_until_2004</t>
+          <t>BLVL_Li-ion_s_12.5 kWh_d_Cavigliano_b_MFH_until_2004</t>
         </is>
       </c>
       <c r="D9" t="n">
-        <v>2</v>
+        <v>0.0125</v>
       </c>
       <c r="E9" t="n">
-        <v>24.96390860179039</v>
+        <v>35.94603160112359</v>
       </c>
       <c r="F9" t="n">
         <v>0</v>
       </c>
       <c r="G9" t="n">
-        <v>18.57013741458328</v>
+        <v>35.94603160112359</v>
       </c>
       <c r="H9" t="n">
         <v>0</v>
       </c>
       <c r="I9" t="n">
-        <v>24.96390860179039</v>
+        <v>26.73951250942907</v>
       </c>
       <c r="J9" t="n">
         <v>0</v>
       </c>
       <c r="K9" t="n">
-        <v>18.57013741458328</v>
+        <v>26.73951250942907</v>
       </c>
     </row>
     <row r="10">
@@ -795,32 +795,32 @@
       </c>
       <c r="C10" t="inlineStr">
         <is>
-          <t>BLVL_VanadiumRedox_s_2 MWh_d_Cavigliano_b_MFH_until_2004</t>
+          <t>BLVL_Li-ion_s_12.5 kWh_d_Cavigliano_b_MFH_until_2004</t>
         </is>
       </c>
       <c r="D10" t="n">
-        <v>2</v>
+        <v>0.0125</v>
       </c>
       <c r="E10" t="n">
-        <v>24.96390860179039</v>
+        <v>35.94603160112359</v>
       </c>
       <c r="F10" t="n">
         <v>0</v>
       </c>
       <c r="G10" t="n">
-        <v>19.24650110018849</v>
+        <v>35.94603160112359</v>
       </c>
       <c r="H10" t="n">
         <v>0</v>
       </c>
       <c r="I10" t="n">
-        <v>24.96390860179039</v>
+        <v>27.71342211647168</v>
       </c>
       <c r="J10" t="n">
         <v>0</v>
       </c>
       <c r="K10" t="n">
-        <v>19.24650110018849</v>
+        <v>27.71342211647168</v>
       </c>
     </row>
     <row r="11">
@@ -832,32 +832,32 @@
       </c>
       <c r="C11" t="inlineStr">
         <is>
-          <t>BLVL_VanadiumRedox_s_2 MWh_d_Cavigliano_b_MFH_until_2004</t>
+          <t>BLVL_Li-ion_s_12.5 kWh_d_Cavigliano_b_MFH_until_2004</t>
         </is>
       </c>
       <c r="D11" t="n">
-        <v>2</v>
+        <v>0.0125</v>
       </c>
       <c r="E11" t="n">
-        <v>24.96390860179039</v>
+        <v>35.94603160112359</v>
       </c>
       <c r="F11" t="n">
         <v>0</v>
       </c>
       <c r="G11" t="n">
-        <v>19.66914119001618</v>
+        <v>35.94603160112359</v>
       </c>
       <c r="H11" t="n">
         <v>0</v>
       </c>
       <c r="I11" t="n">
-        <v>24.96390860179039</v>
+        <v>28.32199004015645</v>
       </c>
       <c r="J11" t="n">
         <v>0</v>
       </c>
       <c r="K11" t="n">
-        <v>19.66914119001618</v>
+        <v>28.32199004015645</v>
       </c>
     </row>
     <row r="12">
@@ -865,7 +865,7 @@
         <v>46023</v>
       </c>
       <c r="B12" t="n">
-        <v>0.006001944137647059</v>
+        <v>0.00521908185882353</v>
       </c>
       <c r="C12" t="inlineStr">
         <is>
@@ -879,19 +879,19 @@
         <v>1</v>
       </c>
       <c r="F12" t="n">
-        <v>0.006001944137647059</v>
+        <v>0.005219081858823535</v>
       </c>
       <c r="G12" t="n">
         <v>1</v>
       </c>
       <c r="H12" t="n">
-        <v>0.006001944137647059</v>
+        <v>0.004958127765882354</v>
       </c>
       <c r="I12" t="n">
         <v>1</v>
       </c>
       <c r="J12" t="n">
-        <v>0.006001944137647059</v>
+        <v>0.005028473412314004</v>
       </c>
       <c r="K12" t="n">
         <v>1</v>
@@ -902,7 +902,7 @@
         <v>47849</v>
       </c>
       <c r="B13" t="n">
-        <v>0.006262898230588236</v>
+        <v>0.005480035951764706</v>
       </c>
       <c r="C13" t="inlineStr">
         <is>
@@ -916,19 +916,19 @@
         <v>1</v>
       </c>
       <c r="F13" t="n">
-        <v>0.006262898230588236</v>
+        <v>0.005480035951764706</v>
       </c>
       <c r="G13" t="n">
         <v>1</v>
       </c>
       <c r="H13" t="n">
-        <v>0.006262898230588236</v>
+        <v>0.004958127765882354</v>
       </c>
       <c r="I13" t="n">
         <v>1</v>
       </c>
       <c r="J13" t="n">
-        <v>0.006262898230588236</v>
+        <v>0.005028473412314004</v>
       </c>
       <c r="K13" t="n">
         <v>1</v>
@@ -939,7 +939,7 @@
         <v>49675</v>
       </c>
       <c r="B14" t="n">
-        <v>0.006262898230588236</v>
+        <v>0.005480035951764706</v>
       </c>
       <c r="C14" t="inlineStr">
         <is>
@@ -953,19 +953,19 @@
         <v>1</v>
       </c>
       <c r="F14" t="n">
-        <v>0.006262898230588236</v>
+        <v>0.005480035951764706</v>
       </c>
       <c r="G14" t="n">
         <v>1</v>
       </c>
       <c r="H14" t="n">
-        <v>0.006262898230588236</v>
+        <v>0.004958127765882354</v>
       </c>
       <c r="I14" t="n">
         <v>1</v>
       </c>
       <c r="J14" t="n">
-        <v>0.006262898230588236</v>
+        <v>0.005028473412314004</v>
       </c>
       <c r="K14" t="n">
         <v>1</v>
@@ -976,7 +976,7 @@
         <v>51502</v>
       </c>
       <c r="B15" t="n">
-        <v>0.006262898230588236</v>
+        <v>0.005480035951764706</v>
       </c>
       <c r="C15" t="inlineStr">
         <is>
@@ -990,19 +990,19 @@
         <v>1</v>
       </c>
       <c r="F15" t="n">
-        <v>0.006262898230588236</v>
+        <v>0.005480035951764706</v>
       </c>
       <c r="G15" t="n">
         <v>1</v>
       </c>
       <c r="H15" t="n">
-        <v>0.006262898230588236</v>
+        <v>0.00521908185882353</v>
       </c>
       <c r="I15" t="n">
         <v>1</v>
       </c>
       <c r="J15" t="n">
-        <v>0.006262898230588236</v>
+        <v>0.00521908185882353</v>
       </c>
       <c r="K15" t="n">
         <v>1</v>
@@ -1013,7 +1013,7 @@
         <v>53328</v>
       </c>
       <c r="B16" t="n">
-        <v>0.006262898230588236</v>
+        <v>0.005480035951764706</v>
       </c>
       <c r="C16" t="inlineStr">
         <is>
@@ -1027,19 +1027,19 @@
         <v>1</v>
       </c>
       <c r="F16" t="n">
-        <v>0.006523852323529413</v>
+        <v>0.005480035951764706</v>
       </c>
       <c r="G16" t="n">
         <v>1</v>
       </c>
       <c r="H16" t="n">
-        <v>0.006262898230588236</v>
+        <v>0.00521908185882353</v>
       </c>
       <c r="I16" t="n">
         <v>1</v>
       </c>
       <c r="J16" t="n">
-        <v>0.006523852323529413</v>
+        <v>0.00521908185882353</v>
       </c>
       <c r="K16" t="n">
         <v>1</v>
@@ -1087,7 +1087,7 @@
         <v>47849</v>
       </c>
       <c r="B18" t="n">
-        <v>0.304990096125</v>
+        <v>0.3408811312695587</v>
       </c>
       <c r="C18" t="inlineStr">
         <is>
@@ -1101,19 +1101,19 @@
         <v>0.9316061117999999</v>
       </c>
       <c r="F18" t="n">
-        <v>0.2678845765155572</v>
+        <v>0.3327164685</v>
       </c>
       <c r="G18" t="n">
         <v>0.9316061117999999</v>
       </c>
       <c r="H18" t="n">
-        <v>0.304990096125</v>
+        <v>0.2537685893295346</v>
       </c>
       <c r="I18" t="n">
         <v>0.9316061117999999</v>
       </c>
       <c r="J18" t="n">
-        <v>0.2678845765155572</v>
+        <v>0.2404884981976135</v>
       </c>
       <c r="K18" t="n">
         <v>0.9316061117999999</v>
@@ -1124,7 +1124,7 @@
         <v>49675</v>
       </c>
       <c r="B19" t="n">
-        <v>0.3233373212655571</v>
+        <v>0.3408811312695587</v>
       </c>
       <c r="C19" t="inlineStr">
         <is>
@@ -1138,19 +1138,19 @@
         <v>0.9316061117999999</v>
       </c>
       <c r="F19" t="n">
-        <v>0.3233373212655571</v>
+        <v>0.3327164685</v>
       </c>
       <c r="G19" t="n">
         <v>0.9316061117999999</v>
       </c>
       <c r="H19" t="n">
-        <v>0.3233373212655572</v>
+        <v>0.2537685893295346</v>
       </c>
       <c r="I19" t="n">
         <v>0.9316061117999999</v>
       </c>
       <c r="J19" t="n">
-        <v>0.3233373212655571</v>
+        <v>0.2404884981976135</v>
       </c>
       <c r="K19" t="n">
         <v>0.9316061117999999</v>
@@ -1161,7 +1161,7 @@
         <v>51502</v>
       </c>
       <c r="B20" t="n">
-        <v>0.3233373212655571</v>
+        <v>0.3408811312695587</v>
       </c>
       <c r="C20" t="inlineStr">
         <is>
@@ -1175,19 +1175,19 @@
         <v>0.9316061117999999</v>
       </c>
       <c r="F20" t="n">
-        <v>0.3233373212655571</v>
+        <v>0.3327164685</v>
       </c>
       <c r="G20" t="n">
         <v>0.9316061117999999</v>
       </c>
       <c r="H20" t="n">
-        <v>0.3233373212655572</v>
+        <v>0.2537685893295346</v>
       </c>
       <c r="I20" t="n">
         <v>0.9316061117999999</v>
       </c>
       <c r="J20" t="n">
-        <v>0.3233373212655571</v>
+        <v>0.2404884981976135</v>
       </c>
       <c r="K20" t="n">
         <v>0.9316061117999999</v>
@@ -1198,7 +1198,7 @@
         <v>53328</v>
       </c>
       <c r="B21" t="n">
-        <v>0.08317911712499995</v>
+        <v>0.27726372375</v>
       </c>
       <c r="C21" t="inlineStr">
         <is>
@@ -1212,19 +1212,19 @@
         <v>0.9316061117999999</v>
       </c>
       <c r="F21" t="n">
-        <v>0.05545274474999997</v>
+        <v>0.27726372375</v>
       </c>
       <c r="G21" t="n">
         <v>0.9316061117999999</v>
       </c>
       <c r="H21" t="n">
-        <v>0.08317911712499995</v>
+        <v>0.204858067160173</v>
       </c>
       <c r="I21" t="n">
         <v>0.9316061117999999</v>
       </c>
       <c r="J21" t="n">
-        <v>0.05545274474999997</v>
+        <v>0.2050519216635927</v>
       </c>
       <c r="K21" t="n">
         <v>0.9316061117999999</v>
@@ -1457,7 +1457,7 @@
         <v>47849</v>
       </c>
       <c r="B28" t="n">
-        <v>0</v>
+        <v>0.027726372375</v>
       </c>
       <c r="C28" t="inlineStr">
         <is>
@@ -1471,19 +1471,19 @@
         <v>0.9316061117999999</v>
       </c>
       <c r="F28" t="n">
-        <v>0</v>
+        <v>0.02772637237499999</v>
       </c>
       <c r="G28" t="n">
         <v>0.9316061117999999</v>
       </c>
       <c r="H28" t="n">
-        <v>0</v>
+        <v>0.1109054894999999</v>
       </c>
       <c r="I28" t="n">
         <v>0.9316061117999999</v>
       </c>
       <c r="J28" t="n">
-        <v>0</v>
+        <v>0.1075223707319321</v>
       </c>
       <c r="K28" t="n">
         <v>0.9316061117999999</v>
@@ -1494,7 +1494,7 @@
         <v>49675</v>
       </c>
       <c r="B29" t="n">
-        <v>0</v>
+        <v>0.027726372375</v>
       </c>
       <c r="C29" t="inlineStr">
         <is>
@@ -1508,19 +1508,19 @@
         <v>0.9316061117999999</v>
       </c>
       <c r="F29" t="n">
-        <v>0</v>
+        <v>0.02772637237499999</v>
       </c>
       <c r="G29" t="n">
         <v>0.9316061117999999</v>
       </c>
       <c r="H29" t="n">
-        <v>0</v>
+        <v>0.1109054894999999</v>
       </c>
       <c r="I29" t="n">
         <v>0.9316061117999999</v>
       </c>
       <c r="J29" t="n">
-        <v>0</v>
+        <v>0.1075223707319321</v>
       </c>
       <c r="K29" t="n">
         <v>0.9316061117999999</v>
@@ -1531,7 +1531,7 @@
         <v>51502</v>
       </c>
       <c r="B30" t="n">
-        <v>0</v>
+        <v>0.027726372375</v>
       </c>
       <c r="C30" t="inlineStr">
         <is>
@@ -1545,19 +1545,19 @@
         <v>0.9316061117999999</v>
       </c>
       <c r="F30" t="n">
-        <v>0</v>
+        <v>0.02772637237499999</v>
       </c>
       <c r="G30" t="n">
         <v>0.9316061117999999</v>
       </c>
       <c r="H30" t="n">
-        <v>0</v>
+        <v>0.1109054894999999</v>
       </c>
       <c r="I30" t="n">
         <v>0.9316061117999999</v>
       </c>
       <c r="J30" t="n">
-        <v>0</v>
+        <v>0.1075223707319321</v>
       </c>
       <c r="K30" t="n">
         <v>0.9316061117999999</v>
@@ -1568,7 +1568,7 @@
         <v>53328</v>
       </c>
       <c r="B31" t="n">
-        <v>0</v>
+        <v>0.027726372375</v>
       </c>
       <c r="C31" t="inlineStr">
         <is>
@@ -1582,19 +1582,19 @@
         <v>0.9316061117999999</v>
       </c>
       <c r="F31" t="n">
-        <v>0</v>
+        <v>0.027726372375</v>
       </c>
       <c r="G31" t="n">
         <v>0.9316061117999999</v>
       </c>
       <c r="H31" t="n">
-        <v>0</v>
+        <v>0.08317911712499995</v>
       </c>
       <c r="I31" t="n">
         <v>0.9316061117999999</v>
       </c>
       <c r="J31" t="n">
-        <v>0</v>
+        <v>0.08317911712499995</v>
       </c>
       <c r="K31" t="n">
         <v>0.9316061117999999</v>
@@ -1992,13 +1992,13 @@
         <v>0</v>
       </c>
       <c r="G42" t="n">
+        <v>11.14191566743122</v>
+      </c>
+      <c r="H42" t="n">
+        <v>0</v>
+      </c>
+      <c r="I42" t="n">
         <v>6.460360892893672</v>
-      </c>
-      <c r="H42" t="n">
-        <v>0</v>
-      </c>
-      <c r="I42" t="n">
-        <v>11.14191566743122</v>
       </c>
       <c r="J42" t="n">
         <v>0</v>
@@ -2029,13 +2029,13 @@
         <v>0</v>
       </c>
       <c r="G43" t="n">
+        <v>11.14191566743122</v>
+      </c>
+      <c r="H43" t="n">
+        <v>0</v>
+      </c>
+      <c r="I43" t="n">
         <v>7.854753115923604</v>
-      </c>
-      <c r="H43" t="n">
-        <v>0</v>
-      </c>
-      <c r="I43" t="n">
-        <v>11.14191566743122</v>
       </c>
       <c r="J43" t="n">
         <v>0</v>
@@ -2066,13 +2066,13 @@
         <v>0</v>
       </c>
       <c r="G44" t="n">
+        <v>11.14191566743122</v>
+      </c>
+      <c r="H44" t="n">
+        <v>0</v>
+      </c>
+      <c r="I44" t="n">
         <v>8.42900286770363</v>
-      </c>
-      <c r="H44" t="n">
-        <v>0</v>
-      </c>
-      <c r="I44" t="n">
-        <v>11.14191566743122</v>
       </c>
       <c r="J44" t="n">
         <v>0</v>
@@ -2103,13 +2103,13 @@
         <v>0</v>
       </c>
       <c r="G45" t="n">
+        <v>11.14191566743122</v>
+      </c>
+      <c r="H45" t="n">
+        <v>0</v>
+      </c>
+      <c r="I45" t="n">
         <v>8.740293107220641</v>
-      </c>
-      <c r="H45" t="n">
-        <v>0</v>
-      </c>
-      <c r="I45" t="n">
-        <v>11.14191566743122</v>
       </c>
       <c r="J45" t="n">
         <v>0</v>
@@ -2140,13 +2140,13 @@
         <v>0</v>
       </c>
       <c r="G46" t="n">
+        <v>11.14191566743122</v>
+      </c>
+      <c r="H46" t="n">
+        <v>0</v>
+      </c>
+      <c r="I46" t="n">
         <v>8.938118828213046</v>
-      </c>
-      <c r="H46" t="n">
-        <v>0</v>
-      </c>
-      <c r="I46" t="n">
-        <v>11.14191566743122</v>
       </c>
       <c r="J46" t="n">
         <v>0</v>
@@ -2345,7 +2345,7 @@
         <v>46023</v>
       </c>
       <c r="B52" t="n">
-        <v>0.4065714883338507</v>
+        <v>0.4221764448884665</v>
       </c>
       <c r="C52" t="inlineStr">
         <is>
@@ -2359,19 +2359,19 @@
         <v>4.613949291096774</v>
       </c>
       <c r="F52" t="n">
-        <v>0.4800553615931906</v>
+        <v>0.3530614685182786</v>
       </c>
       <c r="G52" t="n">
+        <v>4.613949291096774</v>
+      </c>
+      <c r="H52" t="n">
+        <v>0.3842633654254749</v>
+      </c>
+      <c r="I52" t="n">
         <v>1.447649373984813</v>
       </c>
-      <c r="H52" t="n">
-        <v>0.3201609563121541</v>
-      </c>
-      <c r="I52" t="n">
-        <v>4.613949291096774</v>
-      </c>
       <c r="J52" t="n">
-        <v>0.4157671500697657</v>
+        <v>0.3112496316838645</v>
       </c>
       <c r="K52" t="n">
         <v>1.447649373984813</v>
@@ -2382,7 +2382,7 @@
         <v>47849</v>
       </c>
       <c r="B53" t="n">
-        <v>1.320005766284819</v>
+        <v>1.350987117493085</v>
       </c>
       <c r="C53" t="inlineStr">
         <is>
@@ -2396,19 +2396,19 @@
         <v>4.613949291096774</v>
       </c>
       <c r="F53" t="n">
-        <v>1.413674762670898</v>
+        <v>1.272852284439548</v>
       </c>
       <c r="G53" t="n">
+        <v>4.613949291096774</v>
+      </c>
+      <c r="H53" t="n">
+        <v>1.313074038030093</v>
+      </c>
+      <c r="I53" t="n">
         <v>1.90435835320368</v>
       </c>
-      <c r="H53" t="n">
-        <v>1.267958067793109</v>
-      </c>
-      <c r="I53" t="n">
-        <v>4.613949291096774</v>
-      </c>
       <c r="J53" t="n">
-        <v>1.341324238851755</v>
+        <v>1.234354345257034</v>
       </c>
       <c r="K53" t="n">
         <v>1.90435835320368</v>
@@ -2419,7 +2419,7 @@
         <v>49675</v>
       </c>
       <c r="B54" t="n">
-        <v>1.414833933279415</v>
+        <v>1.400261063749332</v>
       </c>
       <c r="C54" t="inlineStr">
         <is>
@@ -2433,19 +2433,19 @@
         <v>4.613949291096774</v>
       </c>
       <c r="F54" t="n">
-        <v>1.47909319249042</v>
+        <v>1.368330274387183</v>
       </c>
       <c r="G54" t="n">
+        <v>4.613949291096774</v>
+      </c>
+      <c r="H54" t="n">
+        <v>1.370998985506049</v>
+      </c>
+      <c r="I54" t="n">
         <v>2.107890351133024</v>
       </c>
-      <c r="H54" t="n">
-        <v>1.363937481350374</v>
-      </c>
-      <c r="I54" t="n">
-        <v>4.613949291096774</v>
-      </c>
       <c r="J54" t="n">
-        <v>1.438086055814703</v>
+        <v>1.331188840709187</v>
       </c>
       <c r="K54" t="n">
         <v>2.107890351133024</v>
@@ -2456,7 +2456,7 @@
         <v>51502</v>
       </c>
       <c r="B55" t="n">
-        <v>1.593294535094202</v>
+        <v>1.540440029050553</v>
       </c>
       <c r="C55" t="inlineStr">
         <is>
@@ -2470,19 +2470,19 @@
         <v>4.613949291096774</v>
       </c>
       <c r="F55" t="n">
-        <v>1.575816576467677</v>
+        <v>1.540440029050552</v>
       </c>
       <c r="G55" t="n">
+        <v>4.613949291096774</v>
+      </c>
+      <c r="H55" t="n">
+        <v>1.547882629545765</v>
+      </c>
+      <c r="I55" t="n">
         <v>2.217732150814591</v>
       </c>
-      <c r="H55" t="n">
-        <v>1.546410521304139</v>
-      </c>
-      <c r="I55" t="n">
-        <v>4.613949291096774</v>
-      </c>
       <c r="J55" t="n">
-        <v>1.55844454011942</v>
+        <v>1.54751936112458</v>
       </c>
       <c r="K55" t="n">
         <v>2.217732150814591</v>
@@ -2493,7 +2493,7 @@
         <v>53328</v>
       </c>
       <c r="B56" t="n">
-        <v>1.498942019842935</v>
+        <v>1.482961958575846</v>
       </c>
       <c r="C56" t="inlineStr">
         <is>
@@ -2507,19 +2507,19 @@
         <v>4.613949291096774</v>
       </c>
       <c r="F56" t="n">
-        <v>1.498942019842935</v>
+        <v>1.432198904251772</v>
       </c>
       <c r="G56" t="n">
+        <v>4.613949291096774</v>
+      </c>
+      <c r="H56" t="n">
+        <v>1.454616279887381</v>
+      </c>
+      <c r="I56" t="n">
         <v>2.285538197130198</v>
       </c>
-      <c r="H56" t="n">
-        <v>1.451374514834375</v>
-      </c>
-      <c r="I56" t="n">
-        <v>4.613949291096774</v>
-      </c>
       <c r="J56" t="n">
-        <v>1.452400799207109</v>
+        <v>1.435778460829457</v>
       </c>
       <c r="K56" t="n">
         <v>2.285538197130198</v>
@@ -2547,13 +2547,13 @@
         <v>0</v>
       </c>
       <c r="G57" t="n">
+        <v>4.613949291096774</v>
+      </c>
+      <c r="H57" t="n">
+        <v>0</v>
+      </c>
+      <c r="I57" t="n">
         <v>1.447649373984813</v>
-      </c>
-      <c r="H57" t="n">
-        <v>0</v>
-      </c>
-      <c r="I57" t="n">
-        <v>4.613949291096774</v>
       </c>
       <c r="J57" t="n">
         <v>0</v>
@@ -2584,13 +2584,13 @@
         <v>0</v>
       </c>
       <c r="G58" t="n">
+        <v>4.613949291096774</v>
+      </c>
+      <c r="H58" t="n">
+        <v>0</v>
+      </c>
+      <c r="I58" t="n">
         <v>1.90435835320368</v>
-      </c>
-      <c r="H58" t="n">
-        <v>0</v>
-      </c>
-      <c r="I58" t="n">
-        <v>4.613949291096774</v>
       </c>
       <c r="J58" t="n">
         <v>0</v>
@@ -2621,13 +2621,13 @@
         <v>0</v>
       </c>
       <c r="G59" t="n">
+        <v>4.613949291096774</v>
+      </c>
+      <c r="H59" t="n">
+        <v>0</v>
+      </c>
+      <c r="I59" t="n">
         <v>2.107890351133024</v>
-      </c>
-      <c r="H59" t="n">
-        <v>0</v>
-      </c>
-      <c r="I59" t="n">
-        <v>4.613949291096774</v>
       </c>
       <c r="J59" t="n">
         <v>0</v>
@@ -2658,13 +2658,13 @@
         <v>0</v>
       </c>
       <c r="G60" t="n">
+        <v>4.613949291096774</v>
+      </c>
+      <c r="H60" t="n">
+        <v>0</v>
+      </c>
+      <c r="I60" t="n">
         <v>2.217732150814591</v>
-      </c>
-      <c r="H60" t="n">
-        <v>0</v>
-      </c>
-      <c r="I60" t="n">
-        <v>4.613949291096774</v>
       </c>
       <c r="J60" t="n">
         <v>0</v>
@@ -2695,13 +2695,13 @@
         <v>0</v>
       </c>
       <c r="G61" t="n">
+        <v>4.613949291096774</v>
+      </c>
+      <c r="H61" t="n">
+        <v>0</v>
+      </c>
+      <c r="I61" t="n">
         <v>2.285538197130198</v>
-      </c>
-      <c r="H61" t="n">
-        <v>0</v>
-      </c>
-      <c r="I61" t="n">
-        <v>4.613949291096774</v>
       </c>
       <c r="J61" t="n">
         <v>0</v>
@@ -2789,7 +2789,7 @@
         <v>49675</v>
       </c>
       <c r="B64" t="n">
-        <v>0.913095271081801</v>
+        <v>0.3131170663707484</v>
       </c>
       <c r="C64" t="inlineStr">
         <is>
@@ -2803,19 +2803,19 @@
         <v>4.613949291096774</v>
       </c>
       <c r="F64" t="n">
-        <v>0.8620990069225519</v>
+        <v>0.3082631901090905</v>
       </c>
       <c r="G64" t="n">
         <v>4.613949291096774</v>
       </c>
       <c r="H64" t="n">
-        <v>0.9416493519381662</v>
+        <v>0.3063865333287329</v>
       </c>
       <c r="I64" t="n">
         <v>4.613949291096774</v>
       </c>
       <c r="J64" t="n">
-        <v>0.9014376627280789</v>
+        <v>0.3092361169869635</v>
       </c>
       <c r="K64" t="n">
         <v>4.613949291096774</v>
@@ -2826,7 +2826,7 @@
         <v>51502</v>
       </c>
       <c r="B65" t="n">
-        <v>0.9900959601958029</v>
+        <v>0.3866663112093811</v>
       </c>
       <c r="C65" t="inlineStr">
         <is>
@@ -2840,19 +2840,19 @@
         <v>4.613949291096774</v>
       </c>
       <c r="F65" t="n">
-        <v>0.9473530406147443</v>
+        <v>0.3885734762830375</v>
       </c>
       <c r="G65" t="n">
         <v>4.613949291096774</v>
       </c>
       <c r="H65" t="n">
-        <v>1.036979973985866</v>
+        <v>0.4245885042322144</v>
       </c>
       <c r="I65" t="n">
         <v>4.613949291096774</v>
       </c>
       <c r="J65" t="n">
-        <v>0.963056596092811</v>
+        <v>0.428551046304358</v>
       </c>
       <c r="K65" t="n">
         <v>4.613949291096774</v>
@@ -2863,7 +2863,7 @@
         <v>53328</v>
       </c>
       <c r="B66" t="n">
-        <v>1.189345489231685</v>
+        <v>0.4417015776978128</v>
       </c>
       <c r="C66" t="inlineStr">
         <is>
@@ -2877,19 +2877,19 @@
         <v>4.613949291096774</v>
       </c>
       <c r="F66" t="n">
-        <v>1.160318214255392</v>
+        <v>0.4944216751066275</v>
       </c>
       <c r="G66" t="n">
         <v>4.613949291096774</v>
       </c>
       <c r="H66" t="n">
-        <v>1.236912994240245</v>
+        <v>0.5133227149021198</v>
       </c>
       <c r="I66" t="n">
         <v>4.613949291096774</v>
       </c>
       <c r="J66" t="n">
-        <v>1.205190954021027</v>
+        <v>0.533299906265586</v>
       </c>
       <c r="K66" t="n">
         <v>4.613949291096774</v>
@@ -3102,7 +3102,7 @@
         <v>0</v>
       </c>
       <c r="G72" t="n">
-        <v>0.1427972631655465</v>
+        <v>4.613949291096774</v>
       </c>
       <c r="H72" t="n">
         <v>0</v>
@@ -3114,7 +3114,7 @@
         <v>0</v>
       </c>
       <c r="K72" t="n">
-        <v>0.1427972631655465</v>
+        <v>4.613949291096774</v>
       </c>
     </row>
     <row r="73">
@@ -3139,7 +3139,7 @@
         <v>0</v>
       </c>
       <c r="G73" t="n">
-        <v>0.2211575721733528</v>
+        <v>4.613949291096774</v>
       </c>
       <c r="H73" t="n">
         <v>0</v>
@@ -3151,7 +3151,7 @@
         <v>0</v>
       </c>
       <c r="K73" t="n">
-        <v>0.2211575721733528</v>
+        <v>4.613949291096774</v>
       </c>
     </row>
     <row r="74">
@@ -3176,7 +3176,7 @@
         <v>0</v>
       </c>
       <c r="G74" t="n">
-        <v>0.2728178587954699</v>
+        <v>4.613949291096774</v>
       </c>
       <c r="H74" t="n">
         <v>0</v>
@@ -3188,7 +3188,7 @@
         <v>0</v>
       </c>
       <c r="K74" t="n">
-        <v>0.2728178587954699</v>
+        <v>4.613949291096774</v>
       </c>
     </row>
     <row r="75">
@@ -3213,7 +3213,7 @@
         <v>0</v>
       </c>
       <c r="G75" t="n">
-        <v>0.3104358664711613</v>
+        <v>4.613949291096774</v>
       </c>
       <c r="H75" t="n">
         <v>0</v>
@@ -3225,7 +3225,7 @@
         <v>0</v>
       </c>
       <c r="K75" t="n">
-        <v>0.3104358664711613</v>
+        <v>4.613949291096774</v>
       </c>
     </row>
     <row r="76">
@@ -3250,7 +3250,7 @@
         <v>0</v>
       </c>
       <c r="G76" t="n">
-        <v>0.3395551135118662</v>
+        <v>4.613949291096774</v>
       </c>
       <c r="H76" t="n">
         <v>0</v>
@@ -3262,7 +3262,7 @@
         <v>0</v>
       </c>
       <c r="K76" t="n">
-        <v>0.3395551135118662</v>
+        <v>4.613949291096774</v>
       </c>
     </row>
     <row r="77">
@@ -3270,7 +3270,7 @@
         <v>46023</v>
       </c>
       <c r="B77" t="n">
-        <v>0.2554612909287894</v>
+        <v>0.2423975792332684</v>
       </c>
       <c r="C77" t="inlineStr">
         <is>
@@ -3284,22 +3284,22 @@
         <v>4.613949291096774</v>
       </c>
       <c r="F77" t="n">
-        <v>0.1819774176694496</v>
+        <v>0.2721129056269137</v>
       </c>
       <c r="G77" t="n">
-        <v>0.1427972631655465</v>
+        <v>4.613949291096774</v>
       </c>
       <c r="H77" t="n">
-        <v>0.2778036620014658</v>
+        <v>0.2803106586962598</v>
       </c>
       <c r="I77" t="n">
         <v>4.613949291096774</v>
       </c>
       <c r="J77" t="n">
-        <v>0.1819774176694496</v>
+        <v>0.3179205720164376</v>
       </c>
       <c r="K77" t="n">
-        <v>0.1427972631655465</v>
+        <v>4.613949291096774</v>
       </c>
     </row>
     <row r="78">
@@ -3307,7 +3307,7 @@
         <v>47849</v>
       </c>
       <c r="B78" t="n">
-        <v>0.2554612909287894</v>
+        <v>0.2423975792332684</v>
       </c>
       <c r="C78" t="inlineStr">
         <is>
@@ -3321,22 +3321,22 @@
         <v>4.613949291096774</v>
       </c>
       <c r="F78" t="n">
-        <v>0.1819774176694496</v>
+        <v>0.2721129056269137</v>
       </c>
       <c r="G78" t="n">
-        <v>0.2211575721733528</v>
+        <v>4.613949291096774</v>
       </c>
       <c r="H78" t="n">
-        <v>0.2778036620014658</v>
+        <v>0.2803106586962598</v>
       </c>
       <c r="I78" t="n">
         <v>4.613949291096774</v>
       </c>
       <c r="J78" t="n">
-        <v>0.1819774176694496</v>
+        <v>0.3179205720164376</v>
       </c>
       <c r="K78" t="n">
-        <v>0.2211575721733528</v>
+        <v>4.613949291096774</v>
       </c>
     </row>
     <row r="79">
@@ -3344,7 +3344,7 @@
         <v>49675</v>
       </c>
       <c r="B79" t="n">
-        <v>0.2554612909287894</v>
+        <v>0.2423975792332684</v>
       </c>
       <c r="C79" t="inlineStr">
         <is>
@@ -3358,22 +3358,22 @@
         <v>4.613949291096774</v>
       </c>
       <c r="F79" t="n">
-        <v>0.1819774176694496</v>
+        <v>0.2721129056269137</v>
       </c>
       <c r="G79" t="n">
-        <v>0.2728178587954699</v>
+        <v>4.613949291096774</v>
       </c>
       <c r="H79" t="n">
-        <v>0.2778036620014658</v>
+        <v>0.2803106586962598</v>
       </c>
       <c r="I79" t="n">
         <v>4.613949291096774</v>
       </c>
       <c r="J79" t="n">
-        <v>0.1819774176694496</v>
+        <v>0.3179205720164376</v>
       </c>
       <c r="K79" t="n">
-        <v>0.2728178587954699</v>
+        <v>4.613949291096774</v>
       </c>
     </row>
     <row r="80">
@@ -3398,7 +3398,7 @@
         <v>0</v>
       </c>
       <c r="G80" t="n">
-        <v>0.3104358664711613</v>
+        <v>4.613949291096774</v>
       </c>
       <c r="H80" t="n">
         <v>0</v>
@@ -3410,7 +3410,7 @@
         <v>0</v>
       </c>
       <c r="K80" t="n">
-        <v>0.3104358664711613</v>
+        <v>4.613949291096774</v>
       </c>
     </row>
     <row r="81">
@@ -3435,7 +3435,7 @@
         <v>0</v>
       </c>
       <c r="G81" t="n">
-        <v>0.3395551135118662</v>
+        <v>4.613949291096774</v>
       </c>
       <c r="H81" t="n">
         <v>0</v>
@@ -3447,7 +3447,7 @@
         <v>0</v>
       </c>
       <c r="K81" t="n">
-        <v>0.3395551135118662</v>
+        <v>4.613949291096774</v>
       </c>
     </row>
     <row r="82">
@@ -3470,13 +3470,13 @@
         <v>0</v>
       </c>
       <c r="G82" t="n">
+        <v>1</v>
+      </c>
+      <c r="H82" t="n">
+        <v>0</v>
+      </c>
+      <c r="I82" t="n">
         <v>0.4293250562242569</v>
-      </c>
-      <c r="H82" t="n">
-        <v>0</v>
-      </c>
-      <c r="I82" t="n">
-        <v>1</v>
       </c>
       <c r="J82" t="n">
         <v>0</v>
@@ -3505,13 +3505,13 @@
         <v>0</v>
       </c>
       <c r="G83" t="n">
+        <v>1</v>
+      </c>
+      <c r="H83" t="n">
+        <v>0</v>
+      </c>
+      <c r="I83" t="n">
         <v>0.5615523961267772</v>
-      </c>
-      <c r="H83" t="n">
-        <v>0</v>
-      </c>
-      <c r="I83" t="n">
-        <v>1</v>
       </c>
       <c r="J83" t="n">
         <v>0</v>
@@ -3540,13 +3540,13 @@
         <v>0</v>
       </c>
       <c r="G84" t="n">
+        <v>1</v>
+      </c>
+      <c r="H84" t="n">
+        <v>0</v>
+      </c>
+      <c r="I84" t="n">
         <v>0.624556919057325</v>
-      </c>
-      <c r="H84" t="n">
-        <v>0</v>
-      </c>
-      <c r="I84" t="n">
-        <v>1</v>
       </c>
       <c r="J84" t="n">
         <v>0</v>
@@ -3575,13 +3575,13 @@
         <v>0</v>
       </c>
       <c r="G85" t="n">
+        <v>1</v>
+      </c>
+      <c r="H85" t="n">
+        <v>0</v>
+      </c>
+      <c r="I85" t="n">
         <v>0.6622379613453093</v>
-      </c>
-      <c r="H85" t="n">
-        <v>0</v>
-      </c>
-      <c r="I85" t="n">
-        <v>1</v>
       </c>
       <c r="J85" t="n">
         <v>0</v>
@@ -3610,13 +3610,13 @@
         <v>0</v>
       </c>
       <c r="G86" t="n">
+        <v>1</v>
+      </c>
+      <c r="H86" t="n">
+        <v>0</v>
+      </c>
+      <c r="I86" t="n">
         <v>0.6881588528152967</v>
-      </c>
-      <c r="H86" t="n">
-        <v>0</v>
-      </c>
-      <c r="I86" t="n">
-        <v>1</v>
       </c>
       <c r="J86" t="n">
         <v>0</v>
@@ -3645,13 +3645,13 @@
         <v>0</v>
       </c>
       <c r="G87" t="n">
+        <v>1</v>
+      </c>
+      <c r="H87" t="n">
+        <v>0</v>
+      </c>
+      <c r="I87" t="n">
         <v>0.4293250562242569</v>
-      </c>
-      <c r="H87" t="n">
-        <v>0</v>
-      </c>
-      <c r="I87" t="n">
-        <v>1</v>
       </c>
       <c r="J87" t="n">
         <v>0</v>
@@ -3680,13 +3680,13 @@
         <v>0</v>
       </c>
       <c r="G88" t="n">
+        <v>1</v>
+      </c>
+      <c r="H88" t="n">
+        <v>0</v>
+      </c>
+      <c r="I88" t="n">
         <v>0.5615523961267772</v>
-      </c>
-      <c r="H88" t="n">
-        <v>0</v>
-      </c>
-      <c r="I88" t="n">
-        <v>1</v>
       </c>
       <c r="J88" t="n">
         <v>0</v>
@@ -3715,13 +3715,13 @@
         <v>0</v>
       </c>
       <c r="G89" t="n">
+        <v>1</v>
+      </c>
+      <c r="H89" t="n">
+        <v>0</v>
+      </c>
+      <c r="I89" t="n">
         <v>0.624556919057325</v>
-      </c>
-      <c r="H89" t="n">
-        <v>0</v>
-      </c>
-      <c r="I89" t="n">
-        <v>1</v>
       </c>
       <c r="J89" t="n">
         <v>0</v>
@@ -3750,13 +3750,13 @@
         <v>0</v>
       </c>
       <c r="G90" t="n">
+        <v>1</v>
+      </c>
+      <c r="H90" t="n">
+        <v>0</v>
+      </c>
+      <c r="I90" t="n">
         <v>0.6622379613453093</v>
-      </c>
-      <c r="H90" t="n">
-        <v>0</v>
-      </c>
-      <c r="I90" t="n">
-        <v>1</v>
       </c>
       <c r="J90" t="n">
         <v>0</v>
@@ -3785,13 +3785,13 @@
         <v>0</v>
       </c>
       <c r="G91" t="n">
+        <v>1</v>
+      </c>
+      <c r="H91" t="n">
+        <v>0</v>
+      </c>
+      <c r="I91" t="n">
         <v>0.6881588528152967</v>
-      </c>
-      <c r="H91" t="n">
-        <v>0</v>
-      </c>
-      <c r="I91" t="n">
-        <v>1</v>
       </c>
       <c r="J91" t="n">
         <v>0</v>
@@ -3820,13 +3820,13 @@
         <v>0</v>
       </c>
       <c r="G92" t="n">
+        <v>1</v>
+      </c>
+      <c r="H92" t="n">
+        <v>0</v>
+      </c>
+      <c r="I92" t="n">
         <v>0.4293250562242569</v>
-      </c>
-      <c r="H92" t="n">
-        <v>0</v>
-      </c>
-      <c r="I92" t="n">
-        <v>1</v>
       </c>
       <c r="J92" t="n">
         <v>0</v>
@@ -3855,13 +3855,13 @@
         <v>0</v>
       </c>
       <c r="G93" t="n">
+        <v>1</v>
+      </c>
+      <c r="H93" t="n">
+        <v>0</v>
+      </c>
+      <c r="I93" t="n">
         <v>0.5615523961267772</v>
-      </c>
-      <c r="H93" t="n">
-        <v>0</v>
-      </c>
-      <c r="I93" t="n">
-        <v>1</v>
       </c>
       <c r="J93" t="n">
         <v>0</v>
@@ -3890,13 +3890,13 @@
         <v>0</v>
       </c>
       <c r="G94" t="n">
+        <v>1</v>
+      </c>
+      <c r="H94" t="n">
+        <v>0</v>
+      </c>
+      <c r="I94" t="n">
         <v>0.624556919057325</v>
-      </c>
-      <c r="H94" t="n">
-        <v>0</v>
-      </c>
-      <c r="I94" t="n">
-        <v>1</v>
       </c>
       <c r="J94" t="n">
         <v>0</v>
@@ -3925,13 +3925,13 @@
         <v>0</v>
       </c>
       <c r="G95" t="n">
+        <v>1</v>
+      </c>
+      <c r="H95" t="n">
+        <v>0</v>
+      </c>
+      <c r="I95" t="n">
         <v>0.6622379613453093</v>
-      </c>
-      <c r="H95" t="n">
-        <v>0</v>
-      </c>
-      <c r="I95" t="n">
-        <v>1</v>
       </c>
       <c r="J95" t="n">
         <v>0</v>
@@ -3960,13 +3960,13 @@
         <v>0</v>
       </c>
       <c r="G96" t="n">
+        <v>1</v>
+      </c>
+      <c r="H96" t="n">
+        <v>0</v>
+      </c>
+      <c r="I96" t="n">
         <v>0.6881588528152967</v>
-      </c>
-      <c r="H96" t="n">
-        <v>0</v>
-      </c>
-      <c r="I96" t="n">
-        <v>1</v>
       </c>
       <c r="J96" t="n">
         <v>0</v>
